--- a/data/gb2762/_gb2762_2025_食品类别_v6.xlsx
+++ b/data/gb2762/_gb2762_2025_食品类别_v6.xlsx
@@ -615,21 +615,9 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>小麦粉制品</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>面筋</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
@@ -812,11 +800,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>豆类蔬菜</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
@@ -858,11 +842,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
@@ -1418,11 +1398,7 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>平菇</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
@@ -1464,11 +1440,7 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>香菇</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
@@ -1510,11 +1482,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>榛蘑</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
@@ -1602,11 +1570,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>松露</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
@@ -1648,11 +1612,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>青头菌</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
@@ -1694,11 +1654,7 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>鸡枞</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
@@ -1740,11 +1696,7 @@
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>鸡油菌</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
@@ -1786,11 +1738,7 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>多汁乳菇</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
@@ -1878,11 +1826,7 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
@@ -2573,11 +2517,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>肉食性鱼类（例如：金枪鱼、金目鲷、枪鱼、鲨鱼等）</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
@@ -2618,11 +2558,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>甲壳类（例如：虾类、蟹类等）</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
@@ -2664,11 +2600,7 @@
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>其他鲜、冻水产动物</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
@@ -2710,16 +2642,8 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>鱼类、甲壳类</t>
@@ -2761,11 +2685,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>肉食性鱼类（例如：金枪鱼、金目鲷、枪鱼、鲨鱼等）</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>鱼类、甲壳类</t>
@@ -2806,11 +2726,7 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>甲壳类（例如：虾类、蟹类等）</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
@@ -3075,7 +2991,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>巴氏杀菌乳</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -3119,11 +3035,7 @@
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
@@ -3165,11 +3077,7 @@
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>生乳</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
@@ -3257,11 +3165,7 @@
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
@@ -4173,11 +4077,7 @@
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>发酵酒（例如：葡萄酒、黄酒、果酒、啤酒等）</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
@@ -4725,7 +4625,11 @@
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>膨化食品</t>
+        </is>
+      </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
@@ -5171,12 +5075,12 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -5224,11 +5128,7 @@
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>大米（粉）</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
@@ -5646,11 +5546,7 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>青头菌</t>
-        </is>
-      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
@@ -5692,11 +5588,7 @@
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>鸡油菌</t>
-        </is>
-      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
@@ -5738,11 +5630,7 @@
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>羊肚菌</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
@@ -5784,11 +5672,7 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>獐头菌</t>
-        </is>
-      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
@@ -5876,11 +5760,7 @@
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>鸡枞</t>
-        </is>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
@@ -5922,11 +5802,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>多汁乳菇</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
@@ -6014,11 +5890,7 @@
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>姬松茸</t>
-        </is>
-      </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
@@ -6106,11 +5978,7 @@
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
@@ -6483,11 +6351,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>肉食性鱼类（例如：金枪鱼、金目鲷、枪鱼、鲨鱼等）</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>鱼类</t>
@@ -7361,12 +7225,12 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>谷物</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -7414,11 +7278,7 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>大米（粉）</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
@@ -7464,11 +7324,7 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>小麦粉（包括食用麸皮）</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
@@ -7514,11 +7370,7 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>玉米粉、玉米糁（渣）</t>
-        </is>
-      </c>
+      <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
@@ -7710,11 +7562,7 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
@@ -7811,7 +7659,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>巴氏杀菌乳</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -7855,11 +7703,7 @@
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
@@ -7901,11 +7745,7 @@
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
@@ -7947,11 +7787,7 @@
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
@@ -7993,11 +7829,7 @@
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>生乳</t>
-        </is>
-      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
@@ -8591,11 +8423,7 @@
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>肉食性鱼类（例如：金枪鱼、金目鲷、枪鱼、鲨鱼等）</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>鱼类及其制品</t>
@@ -8828,11 +8656,7 @@
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr"/>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
@@ -8925,7 +8749,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>巴氏杀菌乳</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -8969,11 +8793,7 @@
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
@@ -9015,11 +8835,7 @@
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
@@ -9061,11 +8877,7 @@
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
@@ -9107,11 +8919,7 @@
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>生乳</t>
-        </is>
-      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
@@ -10027,11 +9835,7 @@
           <t>饮料类</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>饮料类</t>
-        </is>
-      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
@@ -10236,11 +10040,7 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>含氢化和（或）部分氢化油脂的油脂制品</t>
-        </is>
-      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr"/>
       <c r="F210" t="inlineStr">
         <is>
@@ -10331,11 +10131,7 @@
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr">
@@ -10433,7 +10229,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>巴氏杀菌乳</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -10477,11 +10273,7 @@
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr"/>
       <c r="F215" t="inlineStr">
@@ -10523,11 +10315,7 @@
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
@@ -10569,11 +10357,7 @@
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>发酵乳</t>
-        </is>
-      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
@@ -10615,11 +10399,7 @@
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>生乳</t>
-        </is>
-      </c>
+      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
@@ -11008,7 +10788,11 @@
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="inlineStr"/>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>婴儿配方食品</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
@@ -11053,11 +10837,7 @@
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>婴幼儿配方食品</t>
-        </is>
-      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>特殊医学用途婴儿配方食品</t>
@@ -11483,16 +11263,8 @@
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>糙米(包括色稻米)</t>
-        </is>
-      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
@@ -11534,11 +11306,7 @@
       </c>
       <c r="B237" t="inlineStr"/>
       <c r="C237" t="inlineStr"/>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>大米(粉)</t>
-        </is>
-      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
@@ -11579,16 +11347,8 @@
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
@@ -11629,16 +11389,8 @@
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>小麦粉(包括食用麸皮)</t>
-        </is>
-      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
@@ -11679,16 +11431,8 @@
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>谷物</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>玉米</t>
-        </is>
-      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
@@ -11729,16 +11473,8 @@
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>玉米粉、玉米糁(渣)</t>
-        </is>
-      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
@@ -11785,7 +11521,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>肉制品(包括内脏制品、血制品)</t>
+          <t>肉制品（包括内脏制品、血制品）</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -13432,24 +13168,24 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>发酵乳</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.01 mg/kg</t>
+          <t>0.4 mg/kg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -13460,7 +13196,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13476,17 +13212,17 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>生乳</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.1 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -13497,7 +13233,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13513,17 +13249,17 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>铬</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.3mg/kg</t>
+          <t>0.02 mg/kg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -13534,7 +13270,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.123 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13550,17 +13286,17 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02 mg/kg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -13571,7 +13307,7 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13587,17 +13323,17 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02 mg/kg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -13608,7 +13344,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13624,17 +13360,17 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>调制乳、发酵乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.04 mg/kg</t>
+          <t>0.01 mg/kg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -13645,7 +13381,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13656,26 +13392,22 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>巴氏杀菌乳</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.02 mg/kg</t>
+          <t>0.01 mg/kg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -13686,7 +13418,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13744,12 +13476,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.1 mg/kg</t>
+          <t>0.01 mg/kg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -13760,7 +13492,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13781,12 +13513,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>铬</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.3mg/kg</t>
+          <t>0.01 mg/kg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -13797,7 +13529,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.123 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13550,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1 mg/kg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -13834,7 +13566,7 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13855,12 +13587,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1 mg/kg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -13882,26 +13614,22 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>灭菌乳</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.02 mg/kg</t>
+          <t>0.1 mg/kg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -13912,7 +13640,7 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -13933,12 +13661,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01 mg/kg</t>
+          <t>0.1 mg/kg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -13949,7 +13677,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14044,12 +13772,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铬</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3mg/kg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -14060,7 +13788,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.123 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14081,12 +13809,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铬</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3mg/kg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -14097,7 +13825,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.123 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14108,26 +13836,22 @@
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>生乳</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>生乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>铬</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.4 mg/kg</t>
+          <t>0.3mg/kg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -14138,7 +13862,7 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.123 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14154,17 +13878,17 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>生乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铬</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.3mg/kg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -14175,7 +13899,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.123 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14191,17 +13915,17 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.02 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -14212,7 +13936,7 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14233,12 +13957,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0.01 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -14270,12 +13994,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.1 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -14286,7 +14010,7 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14307,12 +14031,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>铬</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.3mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -14323,7 +14047,7 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.123 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14408,37 +14132,33 @@
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>稀奶油、奶油、无水奶油</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>稀奶油、奶油、无水奶油</t>
+          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>苯并[a]芘</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>10μg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>μg/kg</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.27 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14449,11 +14169,7 @@
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>调制乳</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
@@ -14463,12 +14179,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.01 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -14479,7 +14195,7 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14216,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.1 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -14537,12 +14253,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>铬</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.3mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -14553,7 +14269,7 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.123 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14564,33 +14280,37 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>稀奶油、奶油、无水奶油</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>稀奶油、奶油、无水奶油</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>苯并[a]芘</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10μg/kg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>μg/kg</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.27 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14601,22 +14321,26 @@
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>调制乳</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>生乳、巴氏杀菌乳、灭菌乳、调制乳、发酵乳</t>
+          <t>调制乳、发酵乳</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.04 mg/kg</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -14627,7 +14351,7 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14758,7 +14482,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>膨化食品</t>
+          <t>花粉(油菜花粉、松花粉除外)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -14795,17 +14519,17 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>花粉(油菜花粉、松花粉除外)</t>
+          <t>食品(饮料类、婴幼儿配方食品、婴幼儿辅助食品除外)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>锡</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>250 mg/kg</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -14813,10 +14537,14 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.16 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14827,22 +14555,26 @@
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>干菊花</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>食品(饮料类、婴幼儿配方食品、婴幼儿辅助食品除外)</t>
+          <t>干菊花</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>锡</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>250 mg/kg</t>
+          <t>5.0 mg/kg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -14850,14 +14582,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.16 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -14870,14 +14598,14 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>干菊花</t>
+          <t>果冻</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>干菊花</t>
+          <t>果冻</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -14887,7 +14615,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5.0 mg/kg</t>
+          <t>0.4 mg/kg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -14911,14 +14639,14 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>果冻</t>
+          <t>膨化食品</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>果冻</t>
+          <t>膨化食品</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -14928,7 +14656,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.4 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -16154,21 +15882,25 @@
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>棘皮类</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>双壳贝类、腹足类、头足类、棘皮类</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>1.0 mg/kg</t>
+          <t>2.0 mg/kg(去除内脏)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -16179,7 +15911,7 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16193,23 +15925,27 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>棘皮类</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>软体动物</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>双壳贝类</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>双壳贝类、腹足类、头足类、棘皮类</t>
+          <t>双壳贝类</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2.0 mg/kg(去除内脏)</t>
+          <t>1.5 mg/kg</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -16220,7 +15956,7 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16234,23 +15970,27 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>甲壳类（例如：虾类、蟹类等）</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>鱼类</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>肉食性鱼类（例如：金枪鱼、金目鲷、枪鱼、鲨鱼等）</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>枪鱼及其制品</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -16261,7 +16001,7 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16277,17 +16017,17 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>枪鱼及其制品</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1.0 mg/kg</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -16298,7 +16038,7 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16310,29 +16050,21 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>软体动物</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>双壳贝类</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>双壳贝类</t>
+          <t>金枪鱼及其制品</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1.5 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -16343,7 +16075,7 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16355,29 +16087,21 @@
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>鱼类</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>肉食性鱼类（例如：金枪鱼、金目鲷、枪鱼、鲨鱼等）</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>枪鱼及其制品</t>
+          <t>金枪鱼及其制品</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -16404,17 +16128,17 @@
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>枪鱼及其制品</t>
+          <t>金目鲷及其制品</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -16441,17 +16165,17 @@
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>金枪鱼及其制品</t>
+          <t>金目鲷及其制品</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -16478,17 +16202,17 @@
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>金枪鱼及其制品</t>
+          <t>鲨鱼及其制品</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -16515,17 +16239,17 @@
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>金目鲷及其制品</t>
+          <t>鲨鱼及其制品</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -16549,20 +16273,24 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>非肉食性鱼类</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>金目鲷及其制品</t>
+          <t>鱼类</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>0.1 mg/kg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -16573,7 +16301,7 @@
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16663,17 +16391,17 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鱼类、甲壳类</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -16684,7 +16412,7 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16700,17 +16428,17 @@
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鱼类、甲壳类</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0.1 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -16721,7 +16449,7 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16737,17 +16465,17 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1.0 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -16758,7 +16486,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16774,12 +16502,12 @@
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
-          <t>鲨鱼及其制品</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16795,7 +16523,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16811,7 +16539,7 @@
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>鲨鱼及其制品</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -16821,7 +16549,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>0.1 mg/kg</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -16832,7 +16560,7 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16845,19 +16573,15 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>非肉食性鱼类</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>鱼类</t>
+          <t>鱼类及其制品</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16873,7 +16597,7 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16613,7 @@
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>鱼类、甲壳类</t>
+          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -16899,7 +16623,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>1.0 mg/kg</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -16926,17 +16650,17 @@
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.0 mg/kg</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -16947,7 +16671,7 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -16963,17 +16687,17 @@
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>鱼类及其制品</t>
+          <t>鲜、冻水产动物(鱼类、甲壳类、双壳贝类除外)(去除内脏)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0.1 mg/kg</t>
+          <t>1.0 mg/kg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -16984,7 +16708,7 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17321,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>含氢化和（或）部分氢化油脂的油脂制品</t>
+          <t>氢化植物油</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -17636,11 +17360,7 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>氢化植物油</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
@@ -17886,17 +17606,17 @@
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>婴儿配方食品、较大婴儿配方食品、幼儿配方食品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2.0 mg/kg(以固态产品计)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -17904,14 +17624,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17643,7 @@
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>婴儿配方食品、较大婴儿配方食品、幼儿配方食品</t>
+          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -17937,7 +17653,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>100 mg/kg(以固态产品计)</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -17945,14 +17661,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -17968,7 +17680,7 @@
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -18005,7 +17717,7 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品(以水产及动物肝脏为原料的产品除外)</t>
+          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -18042,17 +17754,17 @@
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -18063,7 +17775,7 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18079,17 +17791,17 @@
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品(添加藻类的产品除外)</t>
+          <t>孕妇及乳母营养补充食品</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -18121,12 +17833,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -18137,7 +17849,7 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18158,12 +17870,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -18195,12 +17907,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>100 mg/kg</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -18227,12 +17939,12 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -18264,7 +17976,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>孕妇及乳母营养补充食品</t>
+          <t>添加藻类的产品</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -18274,7 +17986,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>100 mg/kg</t>
+          <t>0.1 mg/kg</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -18285,7 +17997,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18301,17 +18013,17 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -18322,7 +18034,7 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18338,7 +18050,7 @@
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>添加藻类的产品</t>
+          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -18348,7 +18060,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>0.1 mg/kg</t>
+          <t>100 mg/kg</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -18359,7 +18071,7 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18370,22 +18082,26 @@
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -18396,7 +18112,7 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18412,17 +18128,17 @@
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>特殊医学用途配方食品(特殊医学用途婴儿配方食品涉及的品种除外)</t>
+          <t>辅食营养补充品</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>100 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -18433,7 +18149,7 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18444,11 +18160,7 @@
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>其他特殊膳食用食品（例如：辅食营养补充品、运动营养食品、孕妇及乳母营养补充食品等）</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
@@ -18458,12 +18170,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -18474,7 +18186,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18495,12 +18207,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -18532,12 +18244,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>100 mg/kg</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -18564,17 +18276,17 @@
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -18585,7 +18297,7 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18601,17 +18313,17 @@
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>辅食营养补充品</t>
+          <t>运动营养食品(固态、半固态或粉状)</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>100 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -18622,7 +18334,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18643,12 +18355,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -18659,7 +18371,7 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18675,17 +18387,17 @@
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0.05 mg/kg</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -18696,7 +18408,7 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18712,17 +18424,17 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>运动营养食品(固态、半固态或粉状)</t>
+          <t>运动营养食品(液态)</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.2 mg/kg</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -18754,12 +18466,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>0.05 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -18770,7 +18482,7 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18781,17 +18493,21 @@
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>婴幼儿辅助食品</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -18807,7 +18523,7 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18823,12 +18539,12 @@
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>运动营养食品(液态)</t>
+          <t>婴幼儿辅助食品</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -18855,11 +18571,7 @@
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>婴幼儿辅助食品</t>
-        </is>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
@@ -18869,12 +18581,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>锡</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>0.2 mg/kg</t>
+          <t>50 mg/kg</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -18882,10 +18594,14 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.16 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18906,12 +18622,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -18922,7 +18638,7 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18943,12 +18659,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>锡</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>50 mg/kg</t>
+          <t>0.2 mg/kg</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -18956,14 +18672,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.16 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -18984,12 +18696,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>100 mg/kg</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -19012,21 +18724,25 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>婴幼儿罐装辅助食品</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>0.2 mg/kg</t>
+          <t>0.02 mg/kg</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -19037,7 +18753,7 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -19053,17 +18769,17 @@
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>婴幼儿辅助食品</t>
+          <t>婴幼儿罐装辅助食品</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>100 mg/kg</t>
+          <t>2.0 mg/kg(以固态产品计)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -19071,7 +18787,11 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr">
         <is>
           <t>食品按 GB 5009.33 规定的方法测定。</t>
@@ -19086,11 +18806,7 @@
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>婴幼儿罐装辅助食品</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
@@ -19099,12 +18815,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>0.02 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -19136,12 +18852,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2.0 mg/kg(以固态产品计)</t>
+          <t>100 mg/kg(以固态产品计)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -19168,21 +18884,25 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>婴幼儿谷类辅助食品</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.06 mg/kg</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -19193,7 +18913,7 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -19209,17 +18929,17 @@
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>婴幼儿罐装辅助食品</t>
+          <t>婴幼儿谷类辅助食品</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>100 mg/kg(以固态产品计)</t>
+          <t>4.0 mg/kg</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -19227,11 +18947,7 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>食品按 GB 5009.33 规定的方法测定。</t>
@@ -19246,11 +18962,7 @@
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>婴幼儿谷类辅助食品</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
@@ -19259,12 +18971,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>0.06 mg/kg</t>
+          <t>200 mg/kg</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -19275,7 +18987,7 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -19286,22 +18998,26 @@
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>婴幼儿配方食品</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4.0 mg/kg</t>
+          <t>0.08 mg/kg(以固态产品计)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -19309,10 +19025,14 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -19328,17 +19048,17 @@
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
-          <t>婴幼儿谷类辅助食品</t>
+          <t>婴幼儿配方食品</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>锡</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>200 mg/kg</t>
+          <t>50 mg/kg</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -19346,10 +19066,14 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.16 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -19360,11 +19084,7 @@
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>婴幼儿配方食品</t>
-        </is>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
@@ -19374,12 +19094,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>0.08 mg/kg(以固态产品计)</t>
+          <t>2.0 mg/kg(以固态产品计)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -19389,12 +19109,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -19415,12 +19135,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>锡</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>50 mg/kg</t>
+          <t>100 mg/kg(以固态产品计)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -19435,7 +19155,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.16 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -19447,11 +19167,15 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>婴儿配方食品</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>婴儿配方食品、较大婴儿配方食品、幼儿配方食品</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -19492,7 +19216,7 @@
       <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>婴幼儿配方食品</t>
+          <t>婴儿配方食品、较大婴儿配方食品、幼儿配方食品</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -20023,7 +19747,7 @@
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>肉制品(包括内脏制品、血制品)</t>
+          <t>肉制品（包括内脏制品、血制品）</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -20648,7 +20372,7 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>块根和块茎蔬菜（例如：薯类、胡萝卜、萝卜、生姜等）</t>
+          <t>芸薹类蔬菜</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -20687,11 +20411,7 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>芸薹类蔬菜</t>
-        </is>
-      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
@@ -20728,11 +20448,7 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>豆类蔬菜</t>
-        </is>
-      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
@@ -22148,36 +21864,32 @@
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr"/>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>小麦</t>
-        </is>
-      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
+          <t>谷物碾磨加工品</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>苯并[a]芘</t>
+          <t>铬</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>2.0μg/kg</t>
+          <t>1.0mg/kg</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>μg/kg</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.27 规定的方法测定。</t>
+          <t>食品按 GB 5009.123 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22191,34 +21903,38 @@
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>玉米</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
+          <t>稻谷</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>苯并[a]芘</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>2.0μg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>μg/kg</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr"/>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.27 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22230,11 +21946,7 @@
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="inlineStr"/>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>稻谷</t>
-        </is>
-      </c>
+      <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
@@ -22243,12 +21955,12 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.35 mg/kg</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -22279,17 +21991,17 @@
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>稻谷</t>
+          <t>稻谷、糙米、大米(粉)</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>0.35 mg/kg</t>
+          <t>0.2 mg/kg</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -22299,12 +22011,12 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22320,22 +22032,22 @@
       <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
+          <t>稻谷、糙米、大米(粉)</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>苯并[a]芘</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>2.0μg/kg</t>
+          <t>0.2 mg/kg</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>μg/kg</t>
+          <t>mg/kg</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -22345,7 +22057,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.27 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22356,45 +22068,37 @@
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>谷物制品</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>小麦粉制品</t>
-        </is>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>面筋</t>
-        </is>
-      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
+          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>苯并[a]芘</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>2.0μg/kg</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr"/>
+          <t>μg/kg</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.27 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22405,37 +22109,33 @@
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>谷物碾磨加工品</t>
-        </is>
-      </c>
+      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>谷物碾磨加工品</t>
+          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>铬</t>
+          <t>苯并[a]芘</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>1.0mg/kg</t>
+          <t>2.0μg/kg</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>μg/kg</t>
         </is>
       </c>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.123 规定的方法测定。</t>
+          <t>食品按 GB 5009.27 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22447,11 +22147,7 @@
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr"/>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>大米(粉)</t>
-        </is>
-      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
@@ -22488,36 +22184,32 @@
       </c>
       <c r="B241" t="inlineStr"/>
       <c r="C241" t="inlineStr"/>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>大米（粉）</t>
-        </is>
-      </c>
+      <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>苯并[a]芘</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.0μg/kg</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>μg/kg</t>
         </is>
       </c>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.27 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22533,28 +22225,28 @@
       <c r="E242" t="inlineStr"/>
       <c r="F242" t="inlineStr">
         <is>
-          <t>大米(粉)</t>
+          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>苯并[a]芘</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>0.2 mg/kg</t>
+          <t>2.0μg/kg</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>mg/kg</t>
+          <t>μg/kg</t>
         </is>
       </c>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.27 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22570,32 +22262,28 @@
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)</t>
+          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>苯并[a]芘</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>0.2 mg/kg</t>
+          <t>2.0μg/kg</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+          <t>μg/kg</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.27 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22611,32 +22299,28 @@
       <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>苯并[a]芘</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>0.02 mg/kg</t>
+          <t>2.0μg/kg</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>mg/kg</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+          <t>μg/kg</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.27 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22657,12 +22341,12 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02 mg/kg</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -22689,36 +22373,36 @@
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>小麦粉(包括食用麸皮)</t>
-        </is>
-      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr"/>
       <c r="F246" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>苯并[a]芘</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>2.0μg/kg</t>
+          <t>0.02 mg/kg</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>μg/kg</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr"/>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.27 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22730,11 +22414,7 @@
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>小麦粉（包括食用麸皮）</t>
-        </is>
-      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr"/>
       <c r="F247" t="inlineStr">
         <is>
@@ -22784,12 +22464,12 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.02 mg/kg</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -22816,36 +22496,36 @@
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="inlineStr"/>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>玉米粉、玉米糁(渣)</t>
-        </is>
-      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr"/>
       <c r="F249" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>苯并[a]芘</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>2.0μg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>μg/kg</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr"/>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.27 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22857,11 +22537,7 @@
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="inlineStr"/>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>玉米粉、玉米糁（渣）</t>
-        </is>
-      </c>
+      <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
@@ -22870,12 +22546,12 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>0.02 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -22943,36 +22619,36 @@
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>糙米(包括色稻米)</t>
-        </is>
-      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr"/>
       <c r="F252" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、小麦、小麦粉、玉米、玉米粉、玉米糁(渣)</t>
+          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>苯并[a]芘</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>2.0μg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>μg/kg</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr"/>
+          <t>mg/kg</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.27 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -22983,26 +22659,30 @@
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>谷物碾磨加工品</t>
+        </is>
+      </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>糙米（包括色稻米）</t>
+          <t>大米（粉）</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>0.2 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -23010,14 +22690,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -23033,17 +22709,17 @@
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>大米(粉)</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>0.02 mg/kg</t>
+          <t>0.2 mg/kg</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -23051,14 +22727,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -23070,16 +22742,20 @@
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr"/>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>糙米（包括色稻米）</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>稻谷、糙米、大米(粉)、玉米、玉米粉、玉米糁(渣)、小麦、小麦粉</t>
+          <t>糙米</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -23092,14 +22768,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
+      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -23120,12 +22792,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.35 mg/kg</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -23148,21 +22820,25 @@
       </c>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>麦片</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>糙米</t>
+          <t>麦片、面筋、粥类罐头、带馅料面米制品</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>0.35 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -23173,7 +22849,7 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -23185,11 +22861,7 @@
       </c>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>麦片</t>
-        </is>
-      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
@@ -23432,7 +23104,7 @@
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr">
         <is>
-          <t>发酵酒（例如：葡萄酒、黄酒、果酒、啤酒等）</t>
+          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -23471,11 +23143,7 @@
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>蒸馏酒（例如：白酒、白兰地、威士忌、伏特加、朗姆酒等）</t>
-        </is>
-      </c>
+      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
@@ -23784,25 +23452,21 @@
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr"/>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>多汁乳菇</t>
-        </is>
-      </c>
+      <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
-          <t>松茸、牛肝菌、鸡枞、多汁乳菇及以上食用菌的制品</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>1.0 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -23813,7 +23477,7 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -23829,7 +23493,7 @@
       <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -23839,7 +23503,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>1.0 mg/kg(干重计)</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -23862,25 +23526,21 @@
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="inlineStr"/>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>姬松茸</t>
-        </is>
-      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
-          <t>松露、姬松茸及以上食用菌的制品</t>
+          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -23891,7 +23551,7 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -23905,13 +23565,13 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>平菇</t>
+          <t>木耳 （毛木耳,黑木耳）</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -23921,7 +23581,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>1.0 mg/kg</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -23944,11 +23604,7 @@
       </c>
       <c r="B277" t="inlineStr"/>
       <c r="C277" t="inlineStr"/>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>木耳 （毛木耳,黑木耳）</t>
-        </is>
-      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
@@ -24031,12 +23687,12 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>0.1 mg/kg(干重计)</t>
+          <t>0.5 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -24047,7 +23703,7 @@
       <c r="J279" t="inlineStr"/>
       <c r="K279" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24068,12 +23724,12 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -24084,7 +23740,7 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24105,7 +23761,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -24142,12 +23798,12 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>0.5 mg/kg(干重计)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -24170,25 +23826,21 @@
       </c>
       <c r="B283" t="inlineStr"/>
       <c r="C283" t="inlineStr"/>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>松茸</t>
-        </is>
-      </c>
+      <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>松茸、牛肝菌、鸡枞、多汁乳菇及以上食用菌的制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>1.0 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -24199,7 +23851,7 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24215,17 +23867,17 @@
       <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -24236,7 +23888,7 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24252,7 +23904,7 @@
       <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
-          <t>松茸及其制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -24262,7 +23914,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>0.8 mg/kg</t>
+          <t>0.1 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -24273,7 +23925,7 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24289,17 +23941,17 @@
       <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>1.0 mg/kg(干重计)</t>
+          <t>0.5 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -24310,7 +23962,7 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24322,25 +23974,21 @@
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="inlineStr"/>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>松露</t>
-        </is>
-      </c>
+      <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
-          <t>松露、姬松茸及以上食用菌的制品</t>
+          <t>木耳及其制品、银耳及其制品</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>2.0 mg/kg</t>
+          <t>0.5 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -24351,7 +23999,7 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24363,21 +24011,25 @@
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr"/>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>松茸</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>松茸、牛肝菌、鸡枞、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>1.0 mg/kg(干重计)</t>
+          <t>1.0 mg/kg</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -24388,7 +24040,7 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24400,25 +24052,21 @@
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="inlineStr"/>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>榛蘑</t>
-        </is>
-      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+          <t>松茸、牛肝菌、鸡枞、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>1.0 mg/kg</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -24429,7 +24077,7 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24445,7 +24093,7 @@
       <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
-          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
+          <t>松茸、牛肝菌、鸡枞、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -24455,7 +24103,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>1.0 mg/kg</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -24478,25 +24126,21 @@
       </c>
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>獐头菌</t>
-        </is>
-      </c>
+      <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
-          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -24507,7 +24151,7 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24519,25 +24163,21 @@
       </c>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="inlineStr"/>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>羊肚菌</t>
-        </is>
-      </c>
+      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
-          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
+          <t>松茸及其制品</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>0.8 mg/kg</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -24548,7 +24188,7 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24560,15 +24200,11 @@
       </c>
       <c r="B293" t="inlineStr"/>
       <c r="C293" t="inlineStr"/>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>银耳</t>
-        </is>
-      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24578,7 +24214,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>1.0 mg/kg</t>
+          <t>1.0 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -24605,17 +24241,17 @@
       <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>0.5 mg/kg(干重计)</t>
+          <t>1.0 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -24626,7 +24262,7 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24642,17 +24278,17 @@
       <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>0.1 mg/kg(干重计)</t>
+          <t>1.0 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -24663,7 +24299,7 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24679,17 +24315,17 @@
       <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.0 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -24700,7 +24336,7 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24716,17 +24352,17 @@
       <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>0.1 mg/kg(干重计)</t>
+          <t>1.0 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -24737,7 +24373,7 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24753,17 +24389,17 @@
       <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
-          <t>木耳及其制品、银耳及其制品</t>
+          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>0.5 mg/kg(干重计)</t>
+          <t>1.0 mg/kg(干重计)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -24774,7 +24410,7 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24788,23 +24424,23 @@
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>青头菌</t>
+          <t>松露</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>松露、姬松茸及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>1.0 mg/kg(干重计)</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -24815,7 +24451,7 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24467,7 @@
       <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
-          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
+          <t>松露、姬松茸及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24841,7 +24477,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>2.0 mg/kg</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -24866,23 +24502,23 @@
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>香菇</t>
+          <t>榛蘑</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
-          <t>双孢菇、平菇、香菇、榛蘑及以上食用菌的制品</t>
+          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -24893,7 +24529,7 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -24909,7 +24545,7 @@
       <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
-          <t>香菇及其制品</t>
+          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24919,7 +24555,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -24942,15 +24578,11 @@
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>鸡枞</t>
-        </is>
-      </c>
+      <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
-          <t>松茸、牛肝菌、鸡枞、多汁乳菇及以上食用菌的制品</t>
+          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -24960,7 +24592,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>1.0 mg/kg</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -24987,17 +24619,17 @@
       <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>1.0 mg/kg(干重计)</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -25008,7 +24640,7 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25020,25 +24652,21 @@
       </c>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr"/>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>鸡油菌</t>
-        </is>
-      </c>
+      <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
-          <t>牛肝菌、松茸、松露、青头菌、鸡枞、鸡油菌、多汁乳菇及以上食用菌的制品</t>
+          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>1.0 mg/kg(干重计)</t>
+          <t>0.6 mg/kg</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -25049,7 +24677,7 @@
       <c r="J305" t="inlineStr"/>
       <c r="K305" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25061,11 +24689,15 @@
       </c>
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>香菇</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
-          <t>羊肚菌、獐头菌、青头菌、鸡油菌、榛蘑及以上食用菌的制品</t>
+          <t>香菇及其制品</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25075,7 +24707,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>0.6 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -25484,17 +25116,17 @@
       <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
-          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
+          <t>饮料类</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>锡</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>0.3 mg/kg</t>
+          <t>150 mg/kg</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -25502,10 +25134,14 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J317" t="inlineStr"/>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.16 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25516,16 +25152,12 @@
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>包装饮用水</t>
-        </is>
-      </c>
+      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
-          <t>包装饮用水</t>
+          <t>饮料类(包装饮用水、含乳饮料、果蔬汁类及其饮料、固体饮料除外)</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -25535,7 +25167,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>0.01 mg/L</t>
+          <t>0.3 mg/kg</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -25557,7 +25189,11 @@
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
-      <c r="C319" t="inlineStr"/>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>包装饮用水</t>
+        </is>
+      </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
@@ -25567,7 +25203,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>总砷</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -25583,7 +25219,7 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.11 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25604,12 +25240,12 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>总砷</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.01 mg/L</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -25632,25 +25268,21 @@
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>饮用天然矿泉水</t>
-        </is>
-      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
-          <t>饮用天然矿泉水</t>
+          <t>包装饮用水</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>镉</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>0.003 mg/L</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -25661,7 +25293,7 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.15 规定的方法测定。</t>
+          <t>食品按 GB 5009.11 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25673,7 +25305,11 @@
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="inlineStr"/>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>饮用天然矿泉水</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
@@ -25682,12 +25318,12 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>总汞</t>
+          <t>镉</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>0.001 mg/L</t>
+          <t>0.003 mg/L</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -25698,7 +25334,7 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.15 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25719,12 +25355,12 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>亚硝酸盐</t>
+          <t>总汞</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>0.1 mg/L(以NO2-计)</t>
+          <t>0.001 mg/L</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -25735,7 +25371,7 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25756,12 +25392,12 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
+          <t>亚硝酸盐</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.1 mg/L(以NO2-计)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -25772,7 +25408,7 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.17 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25434,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>45 mg/L(以NO3-计)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -25809,7 +25445,7 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.33 规定的方法测定。</t>
+          <t>食品按 GB 5009.17 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25820,30 +25456,22 @@
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>浓缩果蔬汁（浆）</t>
-        </is>
-      </c>
+      <c r="C326" t="inlineStr"/>
+      <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr"/>
       <c r="F326" t="inlineStr">
         <is>
-          <t>浓缩果蔬汁(浆)</t>
+          <t>饮用天然矿泉水</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>甲基汞/无机砷/亚硝酸盐/硝酸盐</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>0.5 mg/kg</t>
+          <t>45 mg/L(以NO3-计)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -25854,7 +25482,7 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.12 规定的方法测定。</t>
+          <t>食品按 GB 5009.33 规定的方法测定。</t>
         </is>
       </c>
     </row>
@@ -25867,18 +25495,18 @@
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="inlineStr">
         <is>
-          <t>蛋白饮料</t>
+          <t>果蔬汁类及其饮料（例如：苹果汁、苹果醋饮料、山楂汁、山楂醋饮料等）</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+          <t>浓缩果蔬汁（浆）</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
       <c r="F327" t="inlineStr">
         <is>
-          <t>含乳饮料</t>
+          <t>浓缩果蔬汁(浆)</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -25888,7 +25516,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>0.05 mg/kg</t>
+          <t>0.5 mg/kg</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -25912,24 +25540,28 @@
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="inlineStr">
         <is>
-          <t>饮料类</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr"/>
+          <t>蛋白饮料</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>含乳饮料（例如：发酵型含乳饮料、配制型含乳饮料、乳酸菌饮料等）</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr"/>
       <c r="F328" t="inlineStr">
         <is>
-          <t>饮料类</t>
+          <t>含乳饮料</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>锡</t>
+          <t>铅</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>150 mg/kg</t>
+          <t>0.05 mg/kg</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -25937,14 +25569,10 @@
           <t>mg/kg</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>食品按 GB 5009.16 规定的方法测定。</t>
+          <t>食品按 GB 5009.12 规定的方法测定。</t>
         </is>
       </c>
     </row>
